--- a/stabilitaet/aufgaben/musterloesung/aufgabe-1.xlsx
+++ b/stabilitaet/aufgaben/musterloesung/aufgabe-1.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maba/sciebo/lehrveranstaltungen/feb/01-unterlagen/03-stabilitaet/aufgaben/musterloesung/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maba/sciebo/lehrveranstaltungen/feb/01-unterlagen/stabilitaet/aufgaben/musterloesung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD01853-B50C-2149-9789-02529E0E4C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08DE0C2-574F-FB49-9B62-D52C3B539876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="760" windowWidth="28680" windowHeight="21580" xr2:uid="{100FF6A7-AEC2-744F-84AD-2D1931DBB6AE}"/>
+    <workbookView xWindow="1080" yWindow="660" windowWidth="33480" windowHeight="21680" xr2:uid="{100FF6A7-AEC2-744F-84AD-2D1931DBB6AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="uuu" localSheetId="0">Sheet1!$C$57:$F$76</definedName>
+    <definedName name="uuu_1" localSheetId="0">Sheet1!$B$57:$E$76</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,8 +39,33 @@
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{E5E83A0A-3E3E-974C-A717-26325A070304}" name="uuu" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/maba/Desktop/uuu.txt" decimal="," thousands=".">
+      <textFields count="4">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="2" xr16:uid="{2133D226-8E65-4D46-A90F-DC04F83663C6}" name="uuu1" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/maba/Desktop/uuu.txt" thousands="." space="1" consecutive="1">
+      <textFields count="4">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
   <si>
     <t xml:space="preserve">A </t>
   </si>
@@ -85,14 +114,36 @@
   <si>
     <t>Green-Lagrange-Verzerrung</t>
   </si>
+  <si>
+    <t>Nichtlinear Handrechnung</t>
+  </si>
+  <si>
+    <t>RFEM Linear</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>RFEM Nichtlinear</t>
+  </si>
+  <si>
+    <t>Iterationen</t>
+  </si>
+  <si>
+    <t>Lastfaktor</t>
+  </si>
+  <si>
+    <t>Last</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000E+00"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -247,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -276,25 +327,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -305,6 +349,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -316,6 +367,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -371,7 +425,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$19:$B$47</c:f>
+              <c:f>Sheet1!$B$20:$B$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
@@ -467,7 +521,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$19:$H$47</c:f>
+              <c:f>Sheet1!$H$20:$H$48</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="29"/>
@@ -564,7 +618,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5B91-AA4C-8A51-C9B69725673D}"/>
+              <c16:uniqueId val="{00000001-93F7-1645-AB20-3DD6E5443AF2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -583,194 +637,98 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$19:$B$47</c:f>
+              <c:f>Sheet1!$L$20:$L$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>-20</c:v>
+                  <c:v>-2388.0597014925374</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-15</c:v>
+                  <c:v>-1791.044776119403</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-10</c:v>
+                  <c:v>-1194.0298507462687</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-5</c:v>
+                  <c:v>-597.01492537313436</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5</c:v>
+                  <c:v>597.01492537313436</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10</c:v>
+                  <c:v>1194.0298507462687</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15</c:v>
+                  <c:v>1791.044776119403</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>20</c:v>
+                  <c:v>2388.0597014925374</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25</c:v>
+                  <c:v>2985.0746268656717</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>30</c:v>
+                  <c:v>3582.0895522388059</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>35</c:v>
+                  <c:v>4179.1044776119406</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>40</c:v>
+                  <c:v>4776.1194029850749</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>45</c:v>
+                  <c:v>5373.1343283582091</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>50</c:v>
+                  <c:v>5970.1492537313434</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>55</c:v>
+                  <c:v>6567.1641791044776</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>60</c:v>
+                  <c:v>7164.1791044776119</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>65</c:v>
+                  <c:v>7761.1940298507461</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>70</c:v>
+                  <c:v>8358.2089552238813</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>75</c:v>
+                  <c:v>8955.2238805970155</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>80</c:v>
+                  <c:v>9552.2388059701498</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>85</c:v>
+                  <c:v>10149.253731343284</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>90</c:v>
+                  <c:v>10746.268656716418</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>95</c:v>
+                  <c:v>11343.283582089553</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>100</c:v>
+                  <c:v>11940.298507462687</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>105</c:v>
+                  <c:v>12537.313432835821</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>110</c:v>
+                  <c:v>13134.328358208955</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>115</c:v>
+                  <c:v>13731.343283582089</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>120</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$K$19:$K$47</c:f>
-              <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="29"/>
-                <c:pt idx="0">
-                  <c:v>-4012.1274369223429</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-2678.6366212697826</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-1577.2134416137587</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-690.22863794489115</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>511.20336661248569</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>861.1567364945015</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1067.6754260090052</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1148.610423598853</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1121.8439922285665</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1005.2852473414933</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>816.8657137609697</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>574.53486499735459</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>296.25564844851453</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>-296.25564844851453</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-574.53486499735459</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-816.8657137609697</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-1005.2852473414933</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-1121.8439922285665</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>-1148.610423598853</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>-1067.6754260090052</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>-861.1567364945015</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>-511.20336661248569</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>690.22863794489115</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1577.2134416137587</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2678.6366212697826</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>4012.1274369223429</c:v>
+                  <c:v>14328.358208955224</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -778,7 +736,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A224-E747-9BD4-34C2C7723036}"/>
+              <c16:uniqueId val="{00000002-93F7-1645-AB20-3DD6E5443AF2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -911,6 +869,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -918,7 +877,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1515,13 +1473,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>482600</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1548,6 +1506,14 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="uuu_1" connectionId="2" xr16:uid="{007B6A6F-D5EF-4847-9FAB-387FFAABB770}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="uuu" connectionId="1" xr16:uid="{219952E7-FDEB-5C40-94D8-A792D6458623}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1867,1685 +1833,2154 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D7B82EC-A16D-C64C-80B6-469F9AFDFA68}">
-  <dimension ref="B2:K267"/>
+  <dimension ref="B1:L267"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="14" t="s">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B1" s="28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B3" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="15"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="30"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C4" s="3">
         <f>40*60</f>
         <v>2400</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="2" t="s">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C5" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C6" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C7" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="4" t="s">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="5">
-        <f>SQRT(C5^2+C6^2)</f>
+      <c r="C8" s="5">
+        <f>SQRT(C6^2+C7^2)</f>
         <v>1001.2492197250393</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="F9" s="31" t="s">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="F10" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="14" t="s">
+      <c r="G10" s="32"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="34"/>
-      <c r="K9" s="15"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="11" t="s">
+      <c r="J10" s="34"/>
+      <c r="K10" s="30"/>
+      <c r="L10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C11" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G11" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H11" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="26" t="s">
+      <c r="I11" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="27" t="s">
+      <c r="J11" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="28" t="s">
+      <c r="K11" s="25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B11" s="30">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="27">
         <v>-20</v>
       </c>
-      <c r="C11" s="29">
-        <f t="shared" ref="C11:C17" si="0">$C$6-B11</f>
+      <c r="C12" s="26">
+        <f t="shared" ref="C12:C18" si="0">$C$7-B12</f>
         <v>70</v>
       </c>
-      <c r="D11" s="17">
-        <f t="shared" ref="D11:D17" si="1">SQRT($C$5^2+C11^2)</f>
+      <c r="D12" s="15">
+        <f t="shared" ref="D12:D18" si="1">SQRT($C$6^2+C12^2)</f>
         <v>1002.4470060806207</v>
       </c>
-      <c r="E11" s="18">
-        <f t="shared" ref="E11:E17" si="2">ATAN(C11/$C$5)</f>
+      <c r="E12" s="16">
+        <f t="shared" ref="E12:E18" si="2">ATAN(C12/$C$6)</f>
         <v>6.9886001634642508E-2</v>
       </c>
-      <c r="F11" s="16">
-        <f t="shared" ref="F11:F17" si="3">(D11-$C$7)/$C$7</f>
+      <c r="F12" s="14">
+        <f t="shared" ref="F12:F18" si="3">(D12-$C$8)/$C$8</f>
         <v>1.1962919241128359E-3</v>
       </c>
-      <c r="G11" s="17">
-        <f t="shared" ref="G11:G17" si="4">$C$3*$C$4*F11</f>
+      <c r="G12" s="15">
+        <f t="shared" ref="G12:G18" si="4">$C$4*$C$5*F12</f>
         <v>28711.006178708059</v>
       </c>
-      <c r="H11" s="17">
-        <f>-2*SIN(E11)*G11</f>
+      <c r="H12" s="15">
+        <f>-2*SIN(E12)*G12</f>
         <v>-4009.7290336920432</v>
       </c>
-      <c r="I11" s="16">
-        <f>0.5*((D11^2-$C$7^2)/$C$7^2)</f>
+      <c r="I12" s="14">
+        <f>0.5*((D12^2-$C$8^2)/$C$8^2)</f>
         <v>1.1970074812966418E-3</v>
       </c>
-      <c r="J11" s="17">
-        <f t="shared" ref="J11:J17" si="5">$C$3*$C$4*I11</f>
+      <c r="J12" s="15">
+        <f t="shared" ref="J12:J18" si="5">$C$4*$C$5*I12</f>
         <v>28728.179551119403</v>
       </c>
-      <c r="K11" s="18">
-        <f>-2*SIN(E11)*J11</f>
+      <c r="K12" s="16">
+        <f>-2*SIN(E12)*J12</f>
         <v>-4012.1274369223429</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="6">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="6">
         <v>0</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C13">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D13" s="18">
         <f t="shared" si="1"/>
         <v>1001.2492197250393</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E13" s="7">
         <f t="shared" si="2"/>
         <v>4.9958395721942765E-2</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F13" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G13" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H12" s="20">
-        <f t="shared" ref="H12:H13" si="6">-2*SIN(E12)*G12</f>
+      <c r="H13" s="18">
+        <f t="shared" ref="H13:H14" si="6">-2*SIN(E13)*G13</f>
         <v>0</v>
       </c>
-      <c r="I12" s="19">
-        <f t="shared" ref="I12:I17" si="7">0.5*((D12^2-$C$7^2)/$C$7^2)</f>
+      <c r="I13" s="17">
+        <f t="shared" ref="I13:I18" si="7">0.5*((D13^2-$C$8^2)/$C$8^2)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J13" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K12" s="7">
-        <f t="shared" ref="K12:K47" si="8">-2*SIN(E12)*J12</f>
+      <c r="K13" s="7">
+        <f t="shared" ref="K13:K48" si="8">-2*SIN(E13)*J13</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="6">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B14" s="6">
         <v>20</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C14">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D14" s="18">
         <f t="shared" si="1"/>
         <v>1000.4498987955369</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E14" s="7">
         <f t="shared" si="2"/>
         <v>2.99910048568779E-2</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F14" s="17">
         <f t="shared" si="3"/>
         <v>-7.9832364785454918E-4</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G14" s="18">
         <f t="shared" si="4"/>
         <v>-19159.767548509179</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H14" s="18">
         <f t="shared" si="6"/>
         <v>1149.0690881118205</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I14" s="17">
         <f t="shared" si="7"/>
         <v>-7.9800498753123002E-4</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J14" s="18">
         <f t="shared" si="5"/>
         <v>-19152.119700749521</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K14" s="7">
         <f t="shared" si="8"/>
         <v>1148.610423598853</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B14" s="6">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="6">
         <v>50</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D15" s="18">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E15" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F15" s="17">
         <f t="shared" si="3"/>
         <v>-1.2476611221553635E-3</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G15" s="18">
         <f t="shared" si="4"/>
         <v>-29943.866931728724</v>
       </c>
-      <c r="H14" s="20">
-        <f t="shared" ref="H14:H17" si="9">-2*SIN(E14)*G14</f>
+      <c r="H15" s="18">
+        <f t="shared" ref="H15:H18" si="9">-2*SIN(E15)*G15</f>
         <v>0</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I15" s="17">
         <f t="shared" si="7"/>
         <v>-1.2468827930175142E-3</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J15" s="18">
         <f t="shared" si="5"/>
         <v>-29925.187032420341</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K15" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B15" s="6">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="6">
         <v>80</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C16">
         <f t="shared" si="0"/>
         <v>-30</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D16" s="18">
         <f t="shared" si="1"/>
         <v>1000.4498987955369</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E16" s="7">
         <f t="shared" si="2"/>
         <v>-2.99910048568779E-2</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F16" s="17">
         <f t="shared" si="3"/>
         <v>-7.9832364785454918E-4</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G16" s="18">
         <f t="shared" si="4"/>
         <v>-19159.767548509179</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H16" s="18">
         <f t="shared" si="9"/>
         <v>-1149.0690881118205</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I16" s="17">
         <f t="shared" si="7"/>
         <v>-7.9800498753123002E-4</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J16" s="18">
         <f t="shared" si="5"/>
         <v>-19152.119700749521</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K16" s="7">
         <f t="shared" si="8"/>
         <v>-1148.610423598853</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B16" s="6">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="6">
         <v>100</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C17">
         <f t="shared" si="0"/>
         <v>-50</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D17" s="18">
         <f t="shared" si="1"/>
         <v>1001.2492197250393</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E17" s="7">
         <f t="shared" si="2"/>
         <v>-4.9958395721942765E-2</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F17" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G17" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H17" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I17" s="17">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J17" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K17" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B17" s="9">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B18" s="9">
         <v>120</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C18" s="10">
         <f t="shared" si="0"/>
         <v>-70</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D18" s="21">
         <f t="shared" si="1"/>
         <v>1002.4470060806207</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E18" s="22">
         <f t="shared" si="2"/>
         <v>-6.9886001634642508E-2</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F18" s="20">
         <f t="shared" si="3"/>
         <v>1.1962919241128359E-3</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G18" s="21">
         <f t="shared" si="4"/>
         <v>28711.006178708059</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H18" s="21">
         <f t="shared" si="9"/>
         <v>4009.7290336920432</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I18" s="20">
         <f t="shared" si="7"/>
         <v>1.1970074812966418E-3</v>
       </c>
-      <c r="J17" s="24">
+      <c r="J18" s="21">
         <f t="shared" si="5"/>
         <v>28728.179551119403</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K18" s="22">
         <f t="shared" si="8"/>
         <v>4012.1274369223429</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B18" s="6"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B19" s="30">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="6"/>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B20" s="27">
         <v>-20</v>
       </c>
-      <c r="C19" s="29">
-        <f t="shared" ref="C19:C47" si="10">$C$6-B19</f>
+      <c r="C20" s="26">
+        <f t="shared" ref="C20:C48" si="10">$C$7-B20</f>
         <v>70</v>
       </c>
-      <c r="D19" s="17">
-        <f t="shared" ref="D19:D47" si="11">SQRT($C$5^2+C19^2)</f>
+      <c r="D20" s="15">
+        <f t="shared" ref="D20:D48" si="11">SQRT($C$6^2+C20^2)</f>
         <v>1002.4470060806207</v>
       </c>
-      <c r="E19" s="18">
-        <f t="shared" ref="E19:E47" si="12">ATAN(C19/$C$5)</f>
+      <c r="E20" s="16">
+        <f t="shared" ref="E20:E48" si="12">ATAN(C20/$C$6)</f>
         <v>6.9886001634642508E-2</v>
       </c>
-      <c r="F19" s="16">
-        <f t="shared" ref="F19:F47" si="13">(D19-$C$7)/$C$7</f>
+      <c r="F20" s="14">
+        <f t="shared" ref="F20:F48" si="13">(D20-$C$8)/$C$8</f>
         <v>1.1962919241128359E-3</v>
       </c>
-      <c r="G19" s="17">
-        <f t="shared" ref="G19:G47" si="14">$C$3*$C$4*F19</f>
+      <c r="G20" s="15">
+        <f t="shared" ref="G20:G48" si="14">$C$4*$C$5*F20</f>
         <v>28711.006178708059</v>
       </c>
-      <c r="H19" s="17">
-        <f>-2*SIN(E19)*G19</f>
+      <c r="H20" s="15">
+        <f>-2*SIN(E20)*G20</f>
         <v>-4009.7290336920432</v>
       </c>
-      <c r="I19" s="16">
-        <f t="shared" ref="I19" si="15">0.5*((D19^2-$C$7^2)/$C$7^2)</f>
+      <c r="I20" s="14">
+        <f t="shared" ref="I20" si="15">0.5*((D20^2-$C$8^2)/$C$8^2)</f>
         <v>1.1970074812966418E-3</v>
       </c>
-      <c r="J19" s="17">
-        <f t="shared" ref="J19" si="16">$C$3*$C$4*I19</f>
+      <c r="J20" s="15">
+        <f t="shared" ref="J20" si="16">$C$4*$C$5*I20</f>
         <v>28728.179551119403</v>
       </c>
-      <c r="K19" s="18">
+      <c r="K20" s="16">
         <f t="shared" si="8"/>
         <v>-4012.1274369223429</v>
       </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B20" s="6">
+      <c r="L20">
+        <f>B20*$D$52</f>
+        <v>-2388.0597014925374</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B21" s="6">
         <v>-15</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C21">
         <f t="shared" si="10"/>
         <v>65</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D21" s="18">
         <f t="shared" si="11"/>
         <v>1002.1102733731453</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E21" s="7">
         <f t="shared" si="12"/>
         <v>6.4908689693433469E-2</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F21" s="17">
         <f t="shared" si="13"/>
         <v>8.5997934494517613E-4</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G21" s="18">
         <f t="shared" si="14"/>
         <v>20639.504278684228</v>
       </c>
-      <c r="H20" s="20">
-        <f t="shared" ref="H20:H47" si="17">-2*SIN(E20)*G20</f>
+      <c r="H21" s="18">
+        <f t="shared" ref="H21:H48" si="17">-2*SIN(E21)*G21</f>
         <v>-2677.4853302295796</v>
       </c>
-      <c r="I20" s="19">
-        <f t="shared" ref="I20:I47" si="18">0.5*((D20^2-$C$7^2)/$C$7^2)</f>
+      <c r="I21" s="17">
+        <f t="shared" ref="I21:I48" si="18">0.5*((D21^2-$C$8^2)/$C$8^2)</f>
         <v>8.6034912718204479E-4</v>
       </c>
-      <c r="J20" s="20">
-        <f t="shared" ref="J20:J47" si="19">$C$3*$C$4*I20</f>
+      <c r="J21" s="18">
+        <f t="shared" ref="J21:J48" si="19">$C$4*$C$5*I21</f>
         <v>20648.379052369073</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K21" s="7">
         <f t="shared" si="8"/>
         <v>-2678.6366212697826</v>
       </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B21" s="6">
+      <c r="L21">
+        <f t="shared" ref="L21:L48" si="20">B21*$D$52</f>
+        <v>-1791.044776119403</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B22" s="6">
         <v>-10</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C22">
         <f t="shared" si="10"/>
         <v>60</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D22" s="18">
         <f t="shared" si="11"/>
         <v>1001.7983829094555</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E22" s="7">
         <f t="shared" si="12"/>
         <v>5.9928155121207881E-2</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F22" s="17">
         <f t="shared" si="13"/>
         <v>5.4847801486130059E-4</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G22" s="18">
         <f t="shared" si="14"/>
         <v>13163.472356671215</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H22" s="18">
         <f t="shared" si="17"/>
         <v>-1576.7810267500847</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I22" s="17">
         <f t="shared" si="18"/>
         <v>5.4862842892768071E-4</v>
       </c>
-      <c r="J21" s="20">
+      <c r="J22" s="18">
         <f t="shared" si="19"/>
         <v>13167.082294264337</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K22" s="7">
         <f t="shared" si="8"/>
         <v>-1577.2134416137587</v>
       </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B22" s="6">
+      <c r="L22">
+        <f t="shared" si="20"/>
+        <v>-1194.0298507462687</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B23" s="6">
         <v>-5</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C23">
         <f t="shared" si="10"/>
         <v>55</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D23" s="18">
         <f t="shared" si="11"/>
         <v>1001.5113578986511</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E23" s="7">
         <f t="shared" si="12"/>
         <v>5.4944642106561366E-2</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F23" s="17">
         <f t="shared" si="13"/>
         <v>2.6181111400394E-4</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G23" s="18">
         <f t="shared" si="14"/>
         <v>6283.4667360945596</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H23" s="18">
         <f t="shared" si="17"/>
         <v>-690.13829500708107</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I23" s="17">
         <f t="shared" si="18"/>
         <v>2.6184538653360772E-4</v>
       </c>
-      <c r="J22" s="20">
+      <c r="J23" s="18">
         <f t="shared" si="19"/>
         <v>6284.2892768065849</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K23" s="7">
         <f t="shared" si="8"/>
         <v>-690.22863794489115</v>
       </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B23" s="6">
+      <c r="L23">
+        <f t="shared" si="20"/>
+        <v>-597.01492537313436</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B24" s="6">
         <v>0</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C24">
         <f t="shared" si="10"/>
         <v>50</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D24" s="18">
         <f t="shared" si="11"/>
         <v>1001.2492197250393</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E24" s="7">
         <f t="shared" si="12"/>
         <v>4.9958395721942765E-2</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F24" s="17">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G24" s="18">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H23" s="20">
+      <c r="H24" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I23" s="19">
+      <c r="I24" s="17">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J23" s="20">
+      <c r="J24" s="18">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K24" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="6">
+      <c r="L24">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="6">
         <v>5</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C25">
         <f t="shared" si="10"/>
         <v>45</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D25" s="18">
         <f t="shared" si="11"/>
         <v>1001.0119879402044</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E25" s="7">
         <f t="shared" si="12"/>
         <v>4.4969661852327585E-2</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F25" s="17">
         <f t="shared" si="13"/>
         <v>-2.3693579995999773E-4</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G25" s="18">
         <f t="shared" si="14"/>
         <v>-5686.4591990399458</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H25" s="18">
         <f t="shared" si="17"/>
         <v>511.26393497713684</v>
       </c>
-      <c r="I24" s="19">
+      <c r="I25" s="17">
         <f t="shared" si="18"/>
         <v>-2.3690773067337474E-4</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J25" s="18">
         <f t="shared" si="19"/>
         <v>-5685.7855361609936</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K25" s="7">
         <f t="shared" si="8"/>
         <v>511.20336661248569</v>
       </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B25" s="6">
+      <c r="L25">
+        <f t="shared" si="20"/>
+        <v>597.01492537313436</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26" s="6">
         <v>10</v>
       </c>
-      <c r="C25" s="21">
+      <c r="C26">
         <f t="shared" si="10"/>
         <v>40</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D26" s="18">
         <f t="shared" si="11"/>
         <v>1000.7996802557443</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E26" s="7">
         <f t="shared" si="12"/>
         <v>3.9978687123290044E-2</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F26" s="17">
         <f t="shared" si="13"/>
         <v>-4.4897859637630478E-4</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G26" s="18">
         <f t="shared" si="14"/>
         <v>-10775.486313031315</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H26" s="18">
         <f t="shared" si="17"/>
         <v>861.35010037395296</v>
       </c>
-      <c r="I25" s="19">
+      <c r="I26" s="17">
         <f t="shared" si="18"/>
         <v>-4.4887780548634232E-4</v>
       </c>
-      <c r="J25" s="20">
+      <c r="J26" s="18">
         <f t="shared" si="19"/>
         <v>-10773.067331672215</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K26" s="7">
         <f t="shared" si="8"/>
         <v>861.1567364945015</v>
       </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B26" s="6">
+      <c r="L26">
+        <f t="shared" si="20"/>
+        <v>1194.0298507462687</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B27" s="6">
         <v>15</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C27">
         <f t="shared" si="10"/>
         <v>35</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D27" s="18">
         <f t="shared" si="11"/>
         <v>1000.6123125366787</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E27" s="7">
         <f t="shared" si="12"/>
         <v>3.4985718828525754E-2</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F27" s="17">
         <f t="shared" si="13"/>
         <v>-6.3611254402328506E-4</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G27" s="18">
         <f t="shared" si="14"/>
         <v>-15266.701056558841</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H27" s="18">
         <f t="shared" si="17"/>
         <v>1068.0151149148942</v>
       </c>
-      <c r="I26" s="19">
+      <c r="I27" s="17">
         <f t="shared" si="18"/>
         <v>-6.3591022443896074E-4</v>
       </c>
-      <c r="J26" s="20">
+      <c r="J27" s="18">
         <f t="shared" si="19"/>
         <v>-15261.845386535058</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K27" s="7">
         <f t="shared" si="8"/>
         <v>1067.6754260090052</v>
       </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B27" s="6">
+      <c r="L27">
+        <f t="shared" si="20"/>
+        <v>1791.044776119403</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B28" s="6">
         <v>20</v>
       </c>
-      <c r="C27" s="21">
+      <c r="C28">
         <f t="shared" si="10"/>
         <v>30</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D28" s="18">
         <f t="shared" si="11"/>
         <v>1000.4498987955369</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E28" s="7">
         <f t="shared" si="12"/>
         <v>2.99910048568779E-2</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F28" s="17">
         <f t="shared" si="13"/>
         <v>-7.9832364785454918E-4</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G28" s="18">
         <f t="shared" si="14"/>
         <v>-19159.767548509179</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H28" s="18">
         <f t="shared" si="17"/>
         <v>1149.0690881118205</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I28" s="17">
         <f t="shared" si="18"/>
         <v>-7.9800498753123002E-4</v>
       </c>
-      <c r="J27" s="20">
+      <c r="J28" s="18">
         <f t="shared" si="19"/>
         <v>-19152.119700749521</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K28" s="7">
         <f t="shared" si="8"/>
         <v>1148.610423598853</v>
       </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B28" s="6">
+      <c r="L28">
+        <f t="shared" si="20"/>
+        <v>2388.0597014925374</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B29" s="6">
         <v>25</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C29">
         <f t="shared" si="10"/>
         <v>25</v>
       </c>
-      <c r="D28" s="20">
+      <c r="D29" s="18">
         <f t="shared" si="11"/>
         <v>1000.3124511871279</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E29" s="7">
         <f t="shared" si="12"/>
         <v>2.4994793618920159E-2</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F29" s="17">
         <f t="shared" si="13"/>
         <v>-9.3559976822625145E-4</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G29" s="18">
         <f t="shared" si="14"/>
         <v>-22454.394437430034</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H29" s="18">
         <f t="shared" si="17"/>
         <v>1122.3690363337037</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I29" s="17">
         <f t="shared" si="18"/>
         <v>-9.3516209476309214E-4</v>
       </c>
-      <c r="J28" s="20">
+      <c r="J29" s="18">
         <f t="shared" si="19"/>
         <v>-22443.89027431421</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K29" s="7">
         <f t="shared" si="8"/>
         <v>1121.8439922285665</v>
       </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B29" s="6">
+      <c r="L29">
+        <f t="shared" si="20"/>
+        <v>2985.0746268656717</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30" s="6">
         <v>30</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C30">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D30" s="18">
         <f t="shared" si="11"/>
         <v>1000.199980003999</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E30" s="7">
         <f t="shared" si="12"/>
         <v>1.9997333973150535E-2</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F30" s="17">
         <f t="shared" si="13"/>
         <v>-1.0479306254325312E-3</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G30" s="18">
         <f t="shared" si="14"/>
         <v>-25150.335010380746</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H30" s="18">
         <f t="shared" si="17"/>
         <v>1005.8122580758377</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I30" s="17">
         <f t="shared" si="18"/>
         <v>-1.0473815461346633E-3</v>
       </c>
-      <c r="J29" s="20">
+      <c r="J30" s="18">
         <f t="shared" si="19"/>
         <v>-25137.15710723192</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K30" s="7">
         <f t="shared" si="8"/>
         <v>1005.2852473414933</v>
       </c>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B30" s="6">
+      <c r="L30">
+        <f t="shared" si="20"/>
+        <v>3582.0895522388059</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31" s="6">
         <v>35</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C31">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
-      <c r="D30" s="20">
+      <c r="D31" s="18">
         <f t="shared" si="11"/>
         <v>1000.1124936725868</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E31" s="7">
         <f t="shared" si="12"/>
         <v>1.4998875151850595E-2</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F31" s="17">
         <f t="shared" si="13"/>
         <v>-1.1353078035503728E-3</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G31" s="18">
         <f t="shared" si="14"/>
         <v>-27247.387285208948</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H31" s="18">
         <f t="shared" si="17"/>
         <v>817.3296741395103</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I31" s="17">
         <f t="shared" si="18"/>
         <v>-1.1346633416460014E-3</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J31" s="18">
         <f t="shared" si="19"/>
         <v>-27231.920199504031</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K31" s="7">
         <f t="shared" si="8"/>
         <v>816.8657137609697</v>
       </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B31" s="6">
+      <c r="L31">
+        <f t="shared" si="20"/>
+        <v>4179.1044776119406</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B32" s="6">
         <v>40</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C32">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="D31" s="20">
+      <c r="D32" s="18">
         <f t="shared" si="11"/>
         <v>1000.0499987500625</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E32" s="7">
         <f t="shared" si="12"/>
         <v>9.9996666866652376E-3</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F32" s="17">
         <f t="shared" si="13"/>
         <v>-1.1977247535894589E-3</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G32" s="18">
         <f t="shared" si="14"/>
         <v>-28745.394086147015</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H32" s="18">
         <f t="shared" si="17"/>
         <v>574.87913848457902</v>
       </c>
-      <c r="I31" s="19">
+      <c r="I32" s="17">
         <f t="shared" si="18"/>
         <v>-1.1970074812968161E-3</v>
       </c>
-      <c r="J31" s="20">
+      <c r="J32" s="18">
         <f t="shared" si="19"/>
         <v>-28728.179551123587</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K32" s="7">
         <f t="shared" si="8"/>
         <v>574.53486499735459</v>
       </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B32" s="6">
+      <c r="L32">
+        <f t="shared" si="20"/>
+        <v>4776.1194029850749</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B33" s="6">
         <v>45</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C33">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D33" s="18">
         <f t="shared" si="11"/>
         <v>1000.0124999218759</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E33" s="7">
         <f t="shared" si="12"/>
         <v>4.9999583339583225E-3</v>
       </c>
-      <c r="F32" s="19">
+      <c r="F33" s="17">
         <f t="shared" si="13"/>
         <v>-1.2351767959459896E-3</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G33" s="18">
         <f t="shared" si="14"/>
         <v>-29644.243102703749</v>
       </c>
-      <c r="H32" s="20">
+      <c r="H33" s="18">
         <f t="shared" si="17"/>
         <v>296.43872556612689</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I33" s="17">
         <f t="shared" si="18"/>
         <v>-1.2344139650873978E-3</v>
       </c>
-      <c r="J32" s="20">
+      <c r="J33" s="18">
         <f t="shared" si="19"/>
         <v>-29625.935162097547</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K33" s="7">
         <f t="shared" si="8"/>
         <v>296.25564844851453</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B33" s="6">
+      <c r="L33">
+        <f t="shared" si="20"/>
+        <v>5373.1343283582091</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B34" s="6">
         <v>50</v>
       </c>
-      <c r="C33" s="21">
+      <c r="C34">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="D33" s="20">
+      <c r="D34" s="18">
         <f t="shared" si="11"/>
         <v>1000</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E34" s="7">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="F33" s="19">
+      <c r="F34" s="17">
         <f t="shared" si="13"/>
         <v>-1.2476611221553635E-3</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G34" s="18">
         <f t="shared" si="14"/>
         <v>-29943.866931728724</v>
       </c>
-      <c r="H33" s="20">
+      <c r="H34" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I34" s="17">
         <f t="shared" si="18"/>
         <v>-1.2468827930175142E-3</v>
       </c>
-      <c r="J33" s="20">
+      <c r="J34" s="18">
         <f t="shared" si="19"/>
         <v>-29925.187032420341</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K34" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B34" s="6">
+      <c r="L34">
+        <f t="shared" si="20"/>
+        <v>5970.1492537313434</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B35" s="6">
         <v>55</v>
       </c>
-      <c r="C34" s="21">
+      <c r="C35">
         <f t="shared" si="10"/>
         <v>-5</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D35" s="18">
         <f t="shared" si="11"/>
         <v>1000.0124999218759</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E35" s="7">
         <f t="shared" si="12"/>
         <v>-4.9999583339583225E-3</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F35" s="17">
         <f t="shared" si="13"/>
         <v>-1.2351767959459896E-3</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G35" s="18">
         <f t="shared" si="14"/>
         <v>-29644.243102703749</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H35" s="18">
         <f t="shared" si="17"/>
         <v>-296.43872556612689</v>
       </c>
-      <c r="I34" s="19">
+      <c r="I35" s="17">
         <f t="shared" si="18"/>
         <v>-1.2344139650873978E-3</v>
       </c>
-      <c r="J34" s="20">
+      <c r="J35" s="18">
         <f t="shared" si="19"/>
         <v>-29625.935162097547</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K35" s="7">
         <f t="shared" si="8"/>
         <v>-296.25564844851453</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B35" s="6">
+      <c r="L35">
+        <f t="shared" si="20"/>
+        <v>6567.1641791044776</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B36" s="6">
         <v>60</v>
       </c>
-      <c r="C35" s="21">
+      <c r="C36">
         <f t="shared" si="10"/>
         <v>-10</v>
       </c>
-      <c r="D35" s="20">
+      <c r="D36" s="18">
         <f t="shared" si="11"/>
         <v>1000.0499987500625</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E36" s="7">
         <f t="shared" si="12"/>
         <v>-9.9996666866652376E-3</v>
       </c>
-      <c r="F35" s="19">
+      <c r="F36" s="17">
         <f t="shared" si="13"/>
         <v>-1.1977247535894589E-3</v>
       </c>
-      <c r="G35" s="20">
+      <c r="G36" s="18">
         <f t="shared" si="14"/>
         <v>-28745.394086147015</v>
       </c>
-      <c r="H35" s="20">
+      <c r="H36" s="18">
         <f t="shared" si="17"/>
         <v>-574.87913848457902</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I36" s="17">
         <f t="shared" si="18"/>
         <v>-1.1970074812968161E-3</v>
       </c>
-      <c r="J35" s="20">
+      <c r="J36" s="18">
         <f t="shared" si="19"/>
         <v>-28728.179551123587</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K36" s="7">
         <f t="shared" si="8"/>
         <v>-574.53486499735459</v>
       </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B36" s="6">
+      <c r="L36">
+        <f t="shared" si="20"/>
+        <v>7164.1791044776119</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B37" s="6">
         <v>65</v>
       </c>
-      <c r="C36" s="21">
+      <c r="C37">
         <f t="shared" si="10"/>
         <v>-15</v>
       </c>
-      <c r="D36" s="20">
+      <c r="D37" s="18">
         <f t="shared" si="11"/>
         <v>1000.1124936725868</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E37" s="7">
         <f t="shared" si="12"/>
         <v>-1.4998875151850595E-2</v>
       </c>
-      <c r="F36" s="19">
+      <c r="F37" s="17">
         <f t="shared" si="13"/>
         <v>-1.1353078035503728E-3</v>
       </c>
-      <c r="G36" s="20">
+      <c r="G37" s="18">
         <f t="shared" si="14"/>
         <v>-27247.387285208948</v>
       </c>
-      <c r="H36" s="20">
+      <c r="H37" s="18">
         <f t="shared" si="17"/>
         <v>-817.3296741395103</v>
       </c>
-      <c r="I36" s="19">
+      <c r="I37" s="17">
         <f t="shared" si="18"/>
         <v>-1.1346633416460014E-3</v>
       </c>
-      <c r="J36" s="20">
+      <c r="J37" s="18">
         <f t="shared" si="19"/>
         <v>-27231.920199504031</v>
       </c>
-      <c r="K36" s="7">
+      <c r="K37" s="7">
         <f t="shared" si="8"/>
         <v>-816.8657137609697</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B37" s="6">
+      <c r="L37">
+        <f t="shared" si="20"/>
+        <v>7761.1940298507461</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B38" s="6">
         <v>70</v>
       </c>
-      <c r="C37" s="21">
+      <c r="C38">
         <f t="shared" si="10"/>
         <v>-20</v>
       </c>
-      <c r="D37" s="20">
+      <c r="D38" s="18">
         <f t="shared" si="11"/>
         <v>1000.199980003999</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E38" s="7">
         <f t="shared" si="12"/>
         <v>-1.9997333973150535E-2</v>
       </c>
-      <c r="F37" s="19">
+      <c r="F38" s="17">
         <f t="shared" si="13"/>
         <v>-1.0479306254325312E-3</v>
       </c>
-      <c r="G37" s="20">
+      <c r="G38" s="18">
         <f t="shared" si="14"/>
         <v>-25150.335010380746</v>
       </c>
-      <c r="H37" s="20">
+      <c r="H38" s="18">
         <f t="shared" si="17"/>
         <v>-1005.8122580758377</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I38" s="17">
         <f t="shared" si="18"/>
         <v>-1.0473815461346633E-3</v>
       </c>
-      <c r="J37" s="20">
+      <c r="J38" s="18">
         <f t="shared" si="19"/>
         <v>-25137.15710723192</v>
       </c>
-      <c r="K37" s="7">
+      <c r="K38" s="7">
         <f t="shared" si="8"/>
         <v>-1005.2852473414933</v>
       </c>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B38" s="6">
+      <c r="L38">
+        <f t="shared" si="20"/>
+        <v>8358.2089552238813</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B39" s="6">
         <v>75</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C39">
         <f t="shared" si="10"/>
         <v>-25</v>
       </c>
-      <c r="D38" s="20">
+      <c r="D39" s="18">
         <f t="shared" si="11"/>
         <v>1000.3124511871279</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E39" s="7">
         <f t="shared" si="12"/>
         <v>-2.4994793618920159E-2</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F39" s="17">
         <f t="shared" si="13"/>
         <v>-9.3559976822625145E-4</v>
       </c>
-      <c r="G38" s="20">
+      <c r="G39" s="18">
         <f t="shared" si="14"/>
         <v>-22454.394437430034</v>
       </c>
-      <c r="H38" s="20">
+      <c r="H39" s="18">
         <f t="shared" si="17"/>
         <v>-1122.3690363337037</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I39" s="17">
         <f t="shared" si="18"/>
         <v>-9.3516209476309214E-4</v>
       </c>
-      <c r="J38" s="20">
+      <c r="J39" s="18">
         <f t="shared" si="19"/>
         <v>-22443.89027431421</v>
       </c>
-      <c r="K38" s="7">
+      <c r="K39" s="7">
         <f t="shared" si="8"/>
         <v>-1121.8439922285665</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B39" s="6">
+      <c r="L39">
+        <f t="shared" si="20"/>
+        <v>8955.2238805970155</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B40" s="6">
         <v>80</v>
       </c>
-      <c r="C39" s="21">
+      <c r="C40">
         <f t="shared" si="10"/>
         <v>-30</v>
       </c>
-      <c r="D39" s="20">
+      <c r="D40" s="18">
         <f t="shared" si="11"/>
         <v>1000.4498987955369</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E40" s="7">
         <f t="shared" si="12"/>
         <v>-2.99910048568779E-2</v>
       </c>
-      <c r="F39" s="19">
+      <c r="F40" s="17">
         <f t="shared" si="13"/>
         <v>-7.9832364785454918E-4</v>
       </c>
-      <c r="G39" s="20">
+      <c r="G40" s="18">
         <f t="shared" si="14"/>
         <v>-19159.767548509179</v>
       </c>
-      <c r="H39" s="20">
+      <c r="H40" s="18">
         <f t="shared" si="17"/>
         <v>-1149.0690881118205</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I40" s="17">
         <f t="shared" si="18"/>
         <v>-7.9800498753123002E-4</v>
       </c>
-      <c r="J39" s="20">
+      <c r="J40" s="18">
         <f t="shared" si="19"/>
         <v>-19152.119700749521</v>
       </c>
-      <c r="K39" s="7">
+      <c r="K40" s="7">
         <f t="shared" si="8"/>
         <v>-1148.610423598853</v>
       </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B40" s="6">
+      <c r="L40">
+        <f t="shared" si="20"/>
+        <v>9552.2388059701498</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B41" s="6">
         <v>85</v>
       </c>
-      <c r="C40" s="21">
+      <c r="C41">
         <f t="shared" si="10"/>
         <v>-35</v>
       </c>
-      <c r="D40" s="20">
+      <c r="D41" s="18">
         <f t="shared" si="11"/>
         <v>1000.6123125366787</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E41" s="7">
         <f t="shared" si="12"/>
         <v>-3.4985718828525754E-2</v>
       </c>
-      <c r="F40" s="19">
+      <c r="F41" s="17">
         <f t="shared" si="13"/>
         <v>-6.3611254402328506E-4</v>
       </c>
-      <c r="G40" s="20">
+      <c r="G41" s="18">
         <f t="shared" si="14"/>
         <v>-15266.701056558841</v>
       </c>
-      <c r="H40" s="20">
+      <c r="H41" s="18">
         <f t="shared" si="17"/>
         <v>-1068.0151149148942</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I41" s="17">
         <f t="shared" si="18"/>
         <v>-6.3591022443896074E-4</v>
       </c>
-      <c r="J40" s="20">
+      <c r="J41" s="18">
         <f t="shared" si="19"/>
         <v>-15261.845386535058</v>
       </c>
-      <c r="K40" s="7">
+      <c r="K41" s="7">
         <f t="shared" si="8"/>
         <v>-1067.6754260090052</v>
       </c>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B41" s="6">
+      <c r="L41">
+        <f t="shared" si="20"/>
+        <v>10149.253731343284</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B42" s="6">
         <v>90</v>
       </c>
-      <c r="C41" s="21">
+      <c r="C42">
         <f t="shared" si="10"/>
         <v>-40</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D42" s="18">
         <f t="shared" si="11"/>
         <v>1000.7996802557443</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E42" s="7">
         <f t="shared" si="12"/>
         <v>-3.9978687123290044E-2</v>
       </c>
-      <c r="F41" s="19">
+      <c r="F42" s="17">
         <f t="shared" si="13"/>
         <v>-4.4897859637630478E-4</v>
       </c>
-      <c r="G41" s="20">
+      <c r="G42" s="18">
         <f t="shared" si="14"/>
         <v>-10775.486313031315</v>
       </c>
-      <c r="H41" s="20">
+      <c r="H42" s="18">
         <f t="shared" si="17"/>
         <v>-861.35010037395296</v>
       </c>
-      <c r="I41" s="19">
+      <c r="I42" s="17">
         <f t="shared" si="18"/>
         <v>-4.4887780548634232E-4</v>
       </c>
-      <c r="J41" s="20">
+      <c r="J42" s="18">
         <f t="shared" si="19"/>
         <v>-10773.067331672215</v>
       </c>
-      <c r="K41" s="7">
+      <c r="K42" s="7">
         <f t="shared" si="8"/>
         <v>-861.1567364945015</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B42" s="6">
+      <c r="L42">
+        <f t="shared" si="20"/>
+        <v>10746.268656716418</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B43" s="6">
         <v>95</v>
       </c>
-      <c r="C42" s="21">
+      <c r="C43">
         <f t="shared" si="10"/>
         <v>-45</v>
       </c>
-      <c r="D42" s="20">
+      <c r="D43" s="18">
         <f t="shared" si="11"/>
         <v>1001.0119879402044</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E43" s="7">
         <f t="shared" si="12"/>
         <v>-4.4969661852327585E-2</v>
       </c>
-      <c r="F42" s="19">
+      <c r="F43" s="17">
         <f t="shared" si="13"/>
         <v>-2.3693579995999773E-4</v>
       </c>
-      <c r="G42" s="20">
+      <c r="G43" s="18">
         <f t="shared" si="14"/>
         <v>-5686.4591990399458</v>
       </c>
-      <c r="H42" s="20">
+      <c r="H43" s="18">
         <f t="shared" si="17"/>
         <v>-511.26393497713684</v>
       </c>
-      <c r="I42" s="19">
+      <c r="I43" s="17">
         <f t="shared" si="18"/>
         <v>-2.3690773067337474E-4</v>
       </c>
-      <c r="J42" s="20">
+      <c r="J43" s="18">
         <f t="shared" si="19"/>
         <v>-5685.7855361609936</v>
       </c>
-      <c r="K42" s="7">
+      <c r="K43" s="7">
         <f t="shared" si="8"/>
         <v>-511.20336661248569</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B43" s="6">
+      <c r="L43">
+        <f t="shared" si="20"/>
+        <v>11343.283582089553</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B44" s="6">
         <v>100</v>
       </c>
-      <c r="C43" s="21">
+      <c r="C44">
         <f t="shared" si="10"/>
         <v>-50</v>
       </c>
-      <c r="D43" s="20">
+      <c r="D44" s="18">
         <f t="shared" si="11"/>
         <v>1001.2492197250393</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E44" s="7">
         <f t="shared" si="12"/>
         <v>-4.9958395721942765E-2</v>
       </c>
-      <c r="F43" s="19">
+      <c r="F44" s="17">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G43" s="20">
+      <c r="G44" s="18">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H43" s="20">
+      <c r="H44" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I43" s="19">
+      <c r="I44" s="17">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J43" s="20">
+      <c r="J44" s="18">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K43" s="7">
+      <c r="K44" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B44" s="6">
+      <c r="L44">
+        <f t="shared" si="20"/>
+        <v>11940.298507462687</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B45" s="6">
         <v>105</v>
       </c>
-      <c r="C44" s="21">
+      <c r="C45">
         <f t="shared" si="10"/>
         <v>-55</v>
       </c>
-      <c r="D44" s="20">
+      <c r="D45" s="18">
         <f t="shared" si="11"/>
         <v>1001.5113578986511</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E45" s="7">
         <f t="shared" si="12"/>
         <v>-5.4944642106561366E-2</v>
       </c>
-      <c r="F44" s="19">
+      <c r="F45" s="17">
         <f t="shared" si="13"/>
         <v>2.6181111400394E-4</v>
       </c>
-      <c r="G44" s="20">
+      <c r="G45" s="18">
         <f t="shared" si="14"/>
         <v>6283.4667360945596</v>
       </c>
-      <c r="H44" s="20">
+      <c r="H45" s="18">
         <f t="shared" si="17"/>
         <v>690.13829500708107</v>
       </c>
-      <c r="I44" s="19">
+      <c r="I45" s="17">
         <f t="shared" si="18"/>
         <v>2.6184538653360772E-4</v>
       </c>
-      <c r="J44" s="20">
+      <c r="J45" s="18">
         <f t="shared" si="19"/>
         <v>6284.2892768065849</v>
       </c>
-      <c r="K44" s="7">
+      <c r="K45" s="7">
         <f t="shared" si="8"/>
         <v>690.22863794489115</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B45" s="6">
+      <c r="L45">
+        <f t="shared" si="20"/>
+        <v>12537.313432835821</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B46" s="6">
         <v>110</v>
       </c>
-      <c r="C45" s="21">
+      <c r="C46">
         <f t="shared" si="10"/>
         <v>-60</v>
       </c>
-      <c r="D45" s="20">
+      <c r="D46" s="18">
         <f t="shared" si="11"/>
         <v>1001.7983829094555</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E46" s="7">
         <f t="shared" si="12"/>
         <v>-5.9928155121207881E-2</v>
       </c>
-      <c r="F45" s="19">
+      <c r="F46" s="17">
         <f t="shared" si="13"/>
         <v>5.4847801486130059E-4</v>
       </c>
-      <c r="G45" s="20">
+      <c r="G46" s="18">
         <f t="shared" si="14"/>
         <v>13163.472356671215</v>
       </c>
-      <c r="H45" s="20">
+      <c r="H46" s="18">
         <f t="shared" si="17"/>
         <v>1576.7810267500847</v>
       </c>
-      <c r="I45" s="19">
+      <c r="I46" s="17">
         <f t="shared" si="18"/>
         <v>5.4862842892768071E-4</v>
       </c>
-      <c r="J45" s="20">
+      <c r="J46" s="18">
         <f t="shared" si="19"/>
         <v>13167.082294264337</v>
       </c>
-      <c r="K45" s="7">
+      <c r="K46" s="7">
         <f t="shared" si="8"/>
         <v>1577.2134416137587</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B46" s="6">
+      <c r="L46">
+        <f t="shared" si="20"/>
+        <v>13134.328358208955</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B47" s="6">
         <v>115</v>
       </c>
-      <c r="C46" s="21">
+      <c r="C47">
         <f t="shared" si="10"/>
         <v>-65</v>
       </c>
-      <c r="D46" s="20">
+      <c r="D47" s="18">
         <f t="shared" si="11"/>
         <v>1002.1102733731453</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E47" s="7">
         <f t="shared" si="12"/>
         <v>-6.4908689693433469E-2</v>
       </c>
-      <c r="F46" s="19">
+      <c r="F47" s="17">
         <f t="shared" si="13"/>
         <v>8.5997934494517613E-4</v>
       </c>
-      <c r="G46" s="20">
+      <c r="G47" s="18">
         <f t="shared" si="14"/>
         <v>20639.504278684228</v>
       </c>
-      <c r="H46" s="20">
+      <c r="H47" s="18">
         <f t="shared" si="17"/>
         <v>2677.4853302295796</v>
       </c>
-      <c r="I46" s="19">
+      <c r="I47" s="17">
         <f t="shared" si="18"/>
         <v>8.6034912718204479E-4</v>
       </c>
-      <c r="J46" s="20">
+      <c r="J47" s="18">
         <f t="shared" si="19"/>
         <v>20648.379052369073</v>
       </c>
-      <c r="K46" s="7">
+      <c r="K47" s="7">
         <f t="shared" si="8"/>
         <v>2678.6366212697826</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B47" s="9">
+      <c r="L47">
+        <f t="shared" si="20"/>
+        <v>13731.343283582089</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B48" s="9">
         <v>120</v>
       </c>
-      <c r="C47" s="10">
+      <c r="C48" s="10">
         <f t="shared" si="10"/>
         <v>-70</v>
       </c>
-      <c r="D47" s="24">
+      <c r="D48" s="21">
         <f t="shared" si="11"/>
         <v>1002.4470060806207</v>
       </c>
-      <c r="E47" s="25">
+      <c r="E48" s="22">
         <f t="shared" si="12"/>
         <v>-6.9886001634642508E-2</v>
       </c>
-      <c r="F47" s="23">
+      <c r="F48" s="20">
         <f t="shared" si="13"/>
         <v>1.1962919241128359E-3</v>
       </c>
-      <c r="G47" s="24">
+      <c r="G48" s="21">
         <f t="shared" si="14"/>
         <v>28711.006178708059</v>
       </c>
-      <c r="H47" s="24">
+      <c r="H48" s="21">
         <f t="shared" si="17"/>
         <v>4009.7290336920432</v>
       </c>
-      <c r="I47" s="23">
+      <c r="I48" s="20">
         <f t="shared" si="18"/>
         <v>1.1970074812966418E-3</v>
       </c>
-      <c r="J47" s="24">
+      <c r="J48" s="21">
         <f t="shared" si="19"/>
         <v>28728.179551119403</v>
       </c>
-      <c r="K47" s="25">
+      <c r="K48" s="22">
         <f t="shared" si="8"/>
         <v>4012.1274369223429</v>
       </c>
-    </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F50"/>
-    </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="L48">
+        <f t="shared" si="20"/>
+        <v>14328.358208955224</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B50" s="28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" t="s">
+        <v>18</v>
+      </c>
       <c r="F51"/>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B52">
+        <v>33.5</v>
+      </c>
+      <c r="C52">
+        <v>4000</v>
+      </c>
+      <c r="D52">
+        <f>C52/B52</f>
+        <v>119.40298507462687</v>
+      </c>
       <c r="F52"/>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F53"/>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F54"/>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55">
+        <v>1.1499999999999999</v>
+      </c>
       <c r="F55"/>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F56"/>
-    </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F57"/>
-    </row>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F58"/>
-    </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F59"/>
-    </row>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F60"/>
-    </row>
-    <row r="61" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F61"/>
-    </row>
-    <row r="62" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F62"/>
-    </row>
-    <row r="63" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F63"/>
-    </row>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F64"/>
-    </row>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F65"/>
-    </row>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F66"/>
-    </row>
-    <row r="67" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F67"/>
-    </row>
-    <row r="68" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F68"/>
-    </row>
-    <row r="69" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F69"/>
-    </row>
-    <row r="70" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F70"/>
-    </row>
-    <row r="71" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F71"/>
-    </row>
-    <row r="72" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F72"/>
-    </row>
-    <row r="73" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F73"/>
-    </row>
-    <row r="74" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F74"/>
-    </row>
-    <row r="75" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F75"/>
-    </row>
-    <row r="76" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F76"/>
-    </row>
-    <row r="77" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="35">
+        <v>3</v>
+      </c>
+      <c r="C57" s="35">
+        <v>0.05</v>
+      </c>
+      <c r="D57" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="E57" s="35">
+        <v>0.05</v>
+      </c>
+      <c r="F57">
+        <f>$E$55*E57</f>
+        <v>5.7499999999999996E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="35">
+        <v>3</v>
+      </c>
+      <c r="C58" s="35">
+        <v>0.1</v>
+      </c>
+      <c r="D58" s="35">
+        <v>1</v>
+      </c>
+      <c r="E58" s="35">
+        <v>0.1</v>
+      </c>
+      <c r="F58">
+        <f t="shared" ref="F58:F76" si="21">$E$55*E58</f>
+        <v>0.11499999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="35">
+        <v>3</v>
+      </c>
+      <c r="C59" s="35">
+        <v>0.15</v>
+      </c>
+      <c r="D59" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="E59" s="35">
+        <v>0.15</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="21"/>
+        <v>0.17249999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="35">
+        <v>3</v>
+      </c>
+      <c r="C60" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="D60" s="35">
+        <v>2</v>
+      </c>
+      <c r="E60" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="21"/>
+        <v>0.22999999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="35">
+        <v>3</v>
+      </c>
+      <c r="C61" s="35">
+        <v>0.25</v>
+      </c>
+      <c r="D61" s="35">
+        <v>2.6</v>
+      </c>
+      <c r="E61" s="35">
+        <v>0.25</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="21"/>
+        <v>0.28749999999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B62" s="35">
+        <v>3</v>
+      </c>
+      <c r="C62" s="35">
+        <v>0.3</v>
+      </c>
+      <c r="D62" s="35">
+        <v>3.2</v>
+      </c>
+      <c r="E62" s="35">
+        <v>0.3</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="21"/>
+        <v>0.34499999999999997</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B63" s="35">
+        <v>3</v>
+      </c>
+      <c r="C63" s="35">
+        <v>0.35</v>
+      </c>
+      <c r="D63" s="35">
+        <v>3.8</v>
+      </c>
+      <c r="E63" s="35">
+        <v>0.35</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="21"/>
+        <v>0.40249999999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B64" s="35">
+        <v>3</v>
+      </c>
+      <c r="C64" s="35">
+        <v>0.4</v>
+      </c>
+      <c r="D64" s="35">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E64" s="35">
+        <v>0.4</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="21"/>
+        <v>0.45999999999999996</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B65" s="35">
+        <v>3</v>
+      </c>
+      <c r="C65" s="35">
+        <v>0.45</v>
+      </c>
+      <c r="D65" s="35">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E65" s="35">
+        <v>0.45</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="21"/>
+        <v>0.51749999999999996</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B66" s="35">
+        <v>3</v>
+      </c>
+      <c r="C66" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="D66" s="35">
+        <v>5.8</v>
+      </c>
+      <c r="E66" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="21"/>
+        <v>0.57499999999999996</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B67" s="35">
+        <v>3</v>
+      </c>
+      <c r="C67" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D67" s="35">
+        <v>6.5</v>
+      </c>
+      <c r="E67" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="21"/>
+        <v>0.63249999999999995</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B68" s="35">
+        <v>3</v>
+      </c>
+      <c r="C68" s="35">
+        <v>0.6</v>
+      </c>
+      <c r="D68" s="35">
+        <v>7.3</v>
+      </c>
+      <c r="E68" s="35">
+        <v>0.6</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="21"/>
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B69" s="35">
+        <v>3</v>
+      </c>
+      <c r="C69" s="35">
+        <v>0.65</v>
+      </c>
+      <c r="D69" s="35">
+        <v>8.1</v>
+      </c>
+      <c r="E69" s="35">
+        <v>0.65</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="21"/>
+        <v>0.74749999999999994</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B70" s="35">
+        <v>3</v>
+      </c>
+      <c r="C70" s="35">
+        <v>0.7</v>
+      </c>
+      <c r="D70" s="35">
+        <v>9</v>
+      </c>
+      <c r="E70" s="35">
+        <v>0.7</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="21"/>
+        <v>0.80499999999999994</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B71" s="35">
+        <v>3</v>
+      </c>
+      <c r="C71" s="35">
+        <v>0.75</v>
+      </c>
+      <c r="D71" s="35">
+        <v>10</v>
+      </c>
+      <c r="E71" s="35">
+        <v>0.75</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="21"/>
+        <v>0.86249999999999993</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B72" s="35">
+        <v>4</v>
+      </c>
+      <c r="C72" s="35">
+        <v>0.8</v>
+      </c>
+      <c r="D72" s="35">
+        <v>11.1</v>
+      </c>
+      <c r="E72" s="35">
+        <v>0.8</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="21"/>
+        <v>0.91999999999999993</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B73" s="35">
+        <v>4</v>
+      </c>
+      <c r="C73" s="35">
+        <v>0.85</v>
+      </c>
+      <c r="D73" s="35">
+        <v>12.4</v>
+      </c>
+      <c r="E73" s="35">
+        <v>0.85</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="21"/>
+        <v>0.97749999999999992</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="35">
+        <v>4</v>
+      </c>
+      <c r="C74" s="35">
+        <v>0.9</v>
+      </c>
+      <c r="D74" s="35">
+        <v>13.9</v>
+      </c>
+      <c r="E74" s="35">
+        <v>0.9</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="21"/>
+        <v>1.0349999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B75" s="35">
+        <v>4</v>
+      </c>
+      <c r="C75" s="35">
+        <v>0.95</v>
+      </c>
+      <c r="D75" s="35">
+        <v>15.9</v>
+      </c>
+      <c r="E75" s="35">
+        <v>0.95</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="21"/>
+        <v>1.0924999999999998</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B76" s="35">
+        <v>6</v>
+      </c>
+      <c r="C76" s="35">
+        <v>1</v>
+      </c>
+      <c r="D76" s="35">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="E76" s="35">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="21"/>
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F77"/>
     </row>
-    <row r="78" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F78"/>
     </row>
-    <row r="79" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F79"/>
     </row>
-    <row r="80" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F80"/>
     </row>
     <row r="81" spans="6:6" x14ac:dyDescent="0.2">
@@ -4111,9 +4546,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:K10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/stabilitaet/aufgaben/musterloesung/aufgabe-1.xlsx
+++ b/stabilitaet/aufgaben/musterloesung/aufgabe-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maba/sciebo/lehrveranstaltungen/feb/01-unterlagen/stabilitaet/aufgaben/musterloesung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08DE0C2-574F-FB49-9B62-D52C3B539876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6E473D-5E61-0B41-9A9A-783A698725F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="660" windowWidth="33480" windowHeight="21680" xr2:uid="{100FF6A7-AEC2-744F-84AD-2D1931DBB6AE}"/>
   </bookViews>
